--- a/artfynd/A 18987-2023 artfynd.xlsx
+++ b/artfynd/A 18987-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18987-2023 artfynd.xlsx
+++ b/artfynd/A 18987-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89565064</v>
+        <v>810334</v>
       </c>
       <c r="B2" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Brännbärberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509425.9592025843</v>
+        <v>509395</v>
       </c>
       <c r="R2" t="n">
-        <v>7156072.015188173</v>
+        <v>7155907</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,35 +765,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Olli Manninen, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89565114</v>
+        <v>810335</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,20 +818,29 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Brännbärberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509622.0996229113</v>
+        <v>509402</v>
       </c>
       <c r="R3" t="n">
-        <v>7156067.892979701</v>
+        <v>7155918</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,23 +881,345 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Sälg, klen högstubbe</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Olli Manninen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Olli Manninen, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>810336</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännbärberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>509494</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7155936</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2007-06-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2007-06-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olli Manninen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olli Manninen, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89565114</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>509622</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7156068</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sälg, klen högstubbe</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89565064</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>509426</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7156072</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 18987-2023 artfynd.xlsx
+++ b/artfynd/A 18987-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/810334</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/810335</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/810336</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565114</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,8 +1249,20 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>